--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_los rios.xlsx
@@ -48,12 +48,12 @@
     <t xml:space="preserve">Mariquina</t>
   </si>
   <si>
+    <t xml:space="preserve">Corral</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lanco</t>
   </si>
   <si>
-    <t xml:space="preserve">Corral</t>
-  </si>
-  <si>
     <t xml:space="preserve">Los Lagos</t>
   </si>
   <si>
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:19</t>
+    <t xml:space="preserve">2026-09-09 23:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -579,7 +579,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>14103</v>
+        <v>14102</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2018</v>
@@ -596,7 +596,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>14102</v>
+        <v>14103</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2018</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:15</t>
+    <t xml:space="preserve">2026-09-17 14:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:10</t>
+    <t xml:space="preserve">2026-09-23 12:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:39</t>
+    <t xml:space="preserve">2026-10-02 13:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:41</t>
+    <t xml:space="preserve">2026-10-05 11:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
